--- a/src/main/resources/Test Datatable.xlsx
+++ b/src/main/resources/Test Datatable.xlsx
@@ -1,26 +1,27 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29628"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\KERJA\Intellij Project\Testing\Testing\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AD8B9E8B-25E2-4695-AF0D-7B3FA66F30F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{29699C2F-5249-4E52-A92E-AD6A0F0A6289}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DATA-INFO" sheetId="1" r:id="rId1"/>
     <sheet name="Datatable" sheetId="2" r:id="rId2"/>
-    <sheet name="dt_Initial Data Entry" sheetId="6" state="hidden" r:id="rId3"/>
-    <sheet name="Inquiry by Status" sheetId="4" r:id="rId4"/>
-    <sheet name="WorkFlow-2" sheetId="5" r:id="rId5"/>
-    <sheet name="WorkFlow-3" sheetId="7" r:id="rId6"/>
-    <sheet name="Backup" sheetId="8" r:id="rId7"/>
-    <sheet name="Xpath" sheetId="3" r:id="rId8"/>
+    <sheet name="Mobile" sheetId="9" r:id="rId3"/>
+    <sheet name="dt_Initial Data Entry" sheetId="6" state="hidden" r:id="rId4"/>
+    <sheet name="XPATH" sheetId="3" r:id="rId5"/>
+    <sheet name="Inquiry by Status" sheetId="4" r:id="rId6"/>
+    <sheet name="WorkFlow-2" sheetId="5" r:id="rId7"/>
+    <sheet name="WorkFlow-3" sheetId="7" r:id="rId8"/>
+    <sheet name="Backup" sheetId="8" r:id="rId9"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -43,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="199" uniqueCount="88">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="267" uniqueCount="112">
   <si>
     <t>Start Data</t>
   </si>
@@ -69,9 +70,6 @@
     <t>Value</t>
   </si>
   <si>
-    <t>start_chrome_driver</t>
-  </si>
-  <si>
     <t>go_to_url</t>
   </si>
   <si>
@@ -114,9 +112,6 @@
     <t>https://172.18.30.165/LOSBTNLOGIN/Login.aspx?menu=0</t>
   </si>
   <si>
-    <t>USER ID</t>
-  </si>
-  <si>
     <t>PASSWORD</t>
   </si>
   <si>
@@ -307,6 +302,85 @@
   </si>
   <si>
     <t>https://developer.bca.co.id/</t>
+  </si>
+  <si>
+    <t>start_new_driver</t>
+  </si>
+  <si>
+    <t>Mobile</t>
+  </si>
+  <si>
+    <t>Skenario Mobile</t>
+  </si>
+  <si>
+    <t>//android.widget.Button[@content-desc="DEVELOPMENT"]</t>
+  </si>
+  <si>
+    <t>btnEnvDevelopment</t>
+  </si>
+  <si>
+    <t>//android.widget.EditText[@hint='Masukan Email PIC']</t>
+  </si>
+  <si>
+    <t>//android.widget.EditText[@hint='Masukan Password']</t>
+  </si>
+  <si>
+    <t>//android.widget.Button[@content-desc="Masuk"]</t>
+  </si>
+  <si>
+    <t>txtEmailPIC</t>
+  </si>
+  <si>
+    <t>txtPasswordPIC</t>
+  </si>
+  <si>
+    <t>btnMasukorLogin</t>
+  </si>
+  <si>
+    <t>screenshot</t>
+  </si>
+  <si>
+    <t>USER ID/EMAIL</t>
+  </si>
+  <si>
+    <t>loudry.tiransri@bankbsn.co.id</t>
+  </si>
+  <si>
+    <t>Batara12345</t>
+  </si>
+  <si>
+    <t>//android.view.View[@content-desc="SP3K"]</t>
+  </si>
+  <si>
+    <t>btnSP3KPIC</t>
+  </si>
+  <si>
+    <t>//android.widget.ImageView[@content-desc="Profil
+Tab 3 of 3"]</t>
+  </si>
+  <si>
+    <t>//android.view.View[@content-desc="Logout"]</t>
+  </si>
+  <si>
+    <t>btnMenuProfil</t>
+  </si>
+  <si>
+    <t>btnLogoutPIC</t>
+  </si>
+  <si>
+    <t>//android.widget.Button[@content-desc="Ya"]</t>
+  </si>
+  <si>
+    <t>btnYaPopupPIC</t>
+  </si>
+  <si>
+    <t>screenshot_full_mobile</t>
+  </si>
+  <si>
+    <t>//android.view.View[@content-desc="Cek Kelayakan"]</t>
+  </si>
+  <si>
+    <t>tombol cek kelayakan</t>
   </si>
 </sst>
 </file>
@@ -403,7 +477,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -415,6 +489,9 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1" quotePrefix="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -712,18 +789,18 @@
         <v>1</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C2" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
     </row>
   </sheetData>
@@ -740,7 +817,7 @@
     <col min="2" max="2" width="15.81640625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="23" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="49.54296875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="8.1796875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.54296875" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="10.453125" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="19.1796875" customWidth="1"/>
     <col min="8" max="8" width="17.1796875" bestFit="1" customWidth="1"/>
@@ -757,31 +834,31 @@
         <v>3</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>23</v>
+        <v>98</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="H1" s="2" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="I1" s="2" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="J1" s="6" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="K1" s="6" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.35">
@@ -789,24 +866,24 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C2" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="F2" s="5" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="G2" s="7"/>
       <c r="H2" s="7"/>
       <c r="I2" s="10" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="J2" s="5"/>
       <c r="K2" s="5"/>
@@ -816,21 +893,21 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="E3" s="7"/>
       <c r="F3" s="7"/>
       <c r="G3" s="5" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="H3" s="8" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="I3" s="8"/>
       <c r="J3" s="5"/>
@@ -841,29 +918,46 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="C4" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="E4" s="7"/>
       <c r="F4" s="7"/>
       <c r="G4" s="5" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="H4" s="8" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="I4" s="8"/>
       <c r="J4" s="5"/>
       <c r="K4" s="5"/>
     </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A5">
+        <v>4</v>
+      </c>
+      <c r="B5" t="s">
+        <v>87</v>
+      </c>
+      <c r="C5" t="s">
+        <v>88</v>
+      </c>
+      <c r="E5" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="F5" t="s">
+        <v>100</v>
+      </c>
+    </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.35">
       <c r="L12" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
     </row>
   </sheetData>
@@ -871,12 +965,238 @@
     <hyperlink ref="G3" r:id="rId1" xr:uid="{00241C0A-274B-437D-B403-A316501FCB38}"/>
     <hyperlink ref="D3" r:id="rId2" xr:uid="{7D62ECF8-D0E4-4CD2-95AC-06C4691A1BCE}"/>
     <hyperlink ref="D4" r:id="rId3" xr:uid="{43AD8348-9BA8-417A-9B8C-EFDD14457260}"/>
+    <hyperlink ref="E5" r:id="rId4" xr:uid="{D81C8870-ABF2-434A-829E-B5B74E6590AD}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{39389EA8-ECC8-4D2B-B1AF-25B9D5B0D7A2}">
+  <dimension ref="A1:F24"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="8.26953125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="9" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="22" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="18" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.54296875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.26953125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" s="3" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A2" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="C2" s="4"/>
+      <c r="D2" s="4"/>
+      <c r="E2" s="4"/>
+      <c r="F2" s="4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="C3" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="C4" t="s">
+        <v>29</v>
+      </c>
+      <c r="D4" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="C5" t="s">
+        <v>27</v>
+      </c>
+      <c r="D5" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="C6" t="s">
+        <v>24</v>
+      </c>
+      <c r="D6" t="s">
+        <v>94</v>
+      </c>
+      <c r="E6" t="str">
+        <f>Datatable!$E$1</f>
+        <v>USER ID/EMAIL</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="C7" t="s">
+        <v>24</v>
+      </c>
+      <c r="D7" t="s">
+        <v>95</v>
+      </c>
+      <c r="E7" t="str">
+        <f>Datatable!$F$1</f>
+        <v>PASSWORD</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="C8" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="C9" t="s">
+        <v>27</v>
+      </c>
+      <c r="D9" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="C10" t="s">
+        <v>29</v>
+      </c>
+      <c r="D10" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="C11" t="s">
+        <v>37</v>
+      </c>
+      <c r="E11" s="9">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="C12" t="s">
+        <v>27</v>
+      </c>
+      <c r="D12" t="s">
+        <v>111</v>
+      </c>
+      <c r="E12" s="9"/>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="C13" t="s">
+        <v>37</v>
+      </c>
+      <c r="E13" s="9">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="C14" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A15" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="C15" s="4"/>
+      <c r="D15" s="4"/>
+      <c r="E15" s="4"/>
+      <c r="F15" s="4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="C16" t="s">
+        <v>27</v>
+      </c>
+      <c r="D16" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="17" spans="3:4" x14ac:dyDescent="0.35">
+      <c r="C17" t="s">
+        <v>29</v>
+      </c>
+      <c r="D17" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="18" spans="3:4" x14ac:dyDescent="0.35">
+      <c r="C18" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="19" spans="3:4" x14ac:dyDescent="0.35">
+      <c r="C19" t="s">
+        <v>27</v>
+      </c>
+      <c r="D19" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="20" spans="3:4" x14ac:dyDescent="0.35">
+      <c r="C20" t="s">
+        <v>29</v>
+      </c>
+      <c r="D20" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="21" spans="3:4" x14ac:dyDescent="0.35">
+      <c r="C21" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="22" spans="3:4" x14ac:dyDescent="0.35">
+      <c r="C22" t="s">
+        <v>27</v>
+      </c>
+      <c r="D22" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="23" spans="3:4" x14ac:dyDescent="0.35">
+      <c r="C23" t="s">
+        <v>29</v>
+      </c>
+      <c r="D23" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="24" spans="3:4" x14ac:dyDescent="0.35">
+      <c r="C24" t="s">
+        <v>109</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{35BD06DC-ED1D-4738-A7E0-2CC2298E6BD6}">
   <dimension ref="A1:B3"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -889,7 +1209,7 @@
         <v>2</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.35">
@@ -897,7 +1217,7 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.35">
@@ -910,7 +1230,101 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
+  <dimension ref="A1:B10"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="18" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="51.1796875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A1" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>90</v>
+      </c>
+      <c r="B2" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>94</v>
+      </c>
+      <c r="B3" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>95</v>
+      </c>
+      <c r="B4" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>96</v>
+      </c>
+      <c r="B5" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
+        <v>102</v>
+      </c>
+      <c r="B6" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
+        <v>105</v>
+      </c>
+      <c r="B7" s="11" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A8" t="s">
+        <v>106</v>
+      </c>
+      <c r="B8" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A9" t="s">
+        <v>108</v>
+      </c>
+      <c r="B9" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A10" t="s">
+        <v>111</v>
+      </c>
+      <c r="B10" t="s">
+        <v>110</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:F44"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -927,7 +1341,7 @@
         <v>4</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C1" s="2" t="s">
         <v>5</v>
@@ -939,31 +1353,31 @@
         <v>7</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="C2" s="4"/>
       <c r="D2" s="4"/>
       <c r="E2" s="4"/>
       <c r="F2" s="4" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.35">
       <c r="C3" t="s">
-        <v>8</v>
+        <v>86</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.35">
       <c r="C4" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E4" t="str">
         <f>Datatable!$D$1</f>
@@ -972,27 +1386,27 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.35">
       <c r="C5" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.35">
       <c r="C6" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="D6" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E6" t="str">
         <f>Datatable!$E$1</f>
-        <v>USER ID</v>
+        <v>USER ID/EMAIL</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.35">
       <c r="C7" t="s">
+        <v>24</v>
+      </c>
+      <c r="D7" t="s">
         <v>26</v>
-      </c>
-      <c r="D7" t="s">
-        <v>28</v>
       </c>
       <c r="E7" t="str">
         <f>Datatable!$F$1</f>
@@ -1001,151 +1415,151 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.35">
       <c r="C8" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.35">
       <c r="C9" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="D9" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.35">
       <c r="C10" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="D10" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.35">
       <c r="C11" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.35">
       <c r="C12" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="D12" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A13" s="1" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="C13" s="4"/>
       <c r="D13" s="4"/>
       <c r="E13" s="4"/>
       <c r="F13" s="4" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.35">
       <c r="C14" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="D14" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.35">
       <c r="C15" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="E15" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.35">
       <c r="C16" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="D16" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
     </row>
     <row r="17" spans="3:5" x14ac:dyDescent="0.35">
       <c r="C17" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="D17" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
     </row>
     <row r="18" spans="3:5" x14ac:dyDescent="0.35">
       <c r="C18" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="D18" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
     </row>
     <row r="19" spans="3:5" x14ac:dyDescent="0.35">
       <c r="C19" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="20" spans="3:5" x14ac:dyDescent="0.35">
       <c r="C20" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="D20" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
     </row>
     <row r="21" spans="3:5" x14ac:dyDescent="0.35">
       <c r="C21" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="D21" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
     </row>
     <row r="22" spans="3:5" x14ac:dyDescent="0.35">
       <c r="C22" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="D22" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
     </row>
     <row r="23" spans="3:5" x14ac:dyDescent="0.35">
       <c r="C23" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="D23" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
     </row>
     <row r="24" spans="3:5" x14ac:dyDescent="0.35">
       <c r="C24" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="D24" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
     </row>
     <row r="25" spans="3:5" x14ac:dyDescent="0.35">
       <c r="C25" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="D25" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
     </row>
     <row r="26" spans="3:5" x14ac:dyDescent="0.35">
       <c r="C26" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="D26" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="E26" t="str">
         <f>Datatable!$I$1</f>
@@ -1154,39 +1568,39 @@
     </row>
     <row r="27" spans="3:5" x14ac:dyDescent="0.35">
       <c r="C27" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="D27" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
     </row>
     <row r="28" spans="3:5" x14ac:dyDescent="0.35">
       <c r="C28" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="E28" s="9" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
     </row>
     <row r="29" spans="3:5" x14ac:dyDescent="0.35">
       <c r="C29" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="E29" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
     </row>
     <row r="30" spans="3:5" x14ac:dyDescent="0.35">
       <c r="C30" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
     </row>
     <row r="31" spans="3:5" x14ac:dyDescent="0.35">
       <c r="C31" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="D31" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="E31" t="str">
         <f>Datatable!$I$1</f>
@@ -1195,109 +1609,109 @@
     </row>
     <row r="32" spans="3:5" x14ac:dyDescent="0.35">
       <c r="C32" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="D32" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.35">
       <c r="C33" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="D33" t="s">
+        <v>74</v>
+      </c>
+      <c r="E33" t="s">
         <v>76</v>
-      </c>
-      <c r="E33" t="s">
-        <v>78</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.35">
       <c r="C34" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="E34" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.35">
       <c r="C35" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="D35" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.35">
       <c r="C36" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="D36" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.35">
       <c r="C37" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="E37" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.35">
       <c r="C38" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.35">
       <c r="C39" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="D39" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A40" s="1" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="C40" s="4"/>
       <c r="D40" s="4"/>
       <c r="E40" s="4"/>
       <c r="F40" s="4" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.35">
       <c r="C41" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="E41" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.35">
       <c r="C42" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="D42" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.35">
       <c r="C43" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="D43" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.35">
       <c r="C44" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
   </sheetData>
@@ -1306,7 +1720,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FE039729-C5F9-4BBD-BD90-0D60E5669C7C}">
   <dimension ref="A1:F44"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -1324,7 +1738,7 @@
         <v>4</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C1" s="2" t="s">
         <v>5</v>
@@ -1336,31 +1750,31 @@
         <v>7</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="C2" s="4"/>
       <c r="D2" s="4"/>
       <c r="E2" s="4"/>
       <c r="F2" s="4" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.35">
       <c r="C3" t="s">
-        <v>8</v>
+        <v>86</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.35">
       <c r="C4" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E4" t="str">
         <f>Datatable!$D$1</f>
@@ -1369,31 +1783,31 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.35">
       <c r="C5" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A6" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="C6" s="4"/>
       <c r="D6" s="4"/>
       <c r="E6" s="4"/>
       <c r="F6" s="4" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.35">
       <c r="C7" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.35">
       <c r="C8" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E8" t="str">
         <f>Datatable!$G$1</f>
@@ -1402,12 +1816,12 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.35">
       <c r="C9" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.35">
       <c r="C10" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="E10" t="str">
         <f>Datatable!$H$1</f>
@@ -1416,34 +1830,34 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.35">
       <c r="C11" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="E11" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.35">
       <c r="C12" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="D12" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="E12" s="9" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.35">
       <c r="C13" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="E13" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
     </row>
     <row r="44" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B44" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
     </row>
   </sheetData>
@@ -1451,7 +1865,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2E0C5BB5-9CEB-45E6-8488-333DBE1EF9A7}">
   <dimension ref="A1:F8"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -1469,7 +1883,7 @@
         <v>4</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C1" s="2" t="s">
         <v>5</v>
@@ -1481,31 +1895,31 @@
         <v>7</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="C2" s="4"/>
       <c r="D2" s="4"/>
       <c r="E2" s="4"/>
       <c r="F2" s="4" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.35">
       <c r="C3" t="s">
-        <v>8</v>
+        <v>86</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.35">
       <c r="C4" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E4" t="str">
         <f>Datatable!$D$1</f>
@@ -1514,26 +1928,26 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.35">
       <c r="C5" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A6" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="C6" s="4"/>
       <c r="D6" s="4"/>
       <c r="E6" s="4"/>
       <c r="F6" s="4" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.35">
       <c r="C7" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E7" t="str">
         <f>Datatable!$G$1</f>
@@ -1542,7 +1956,7 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.35">
       <c r="C8" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
     </row>
   </sheetData>
@@ -1550,7 +1964,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4254AE48-397C-42B8-BD99-22BF9380EC1F}">
   <dimension ref="C1:E17"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -1560,47 +1974,47 @@
   <sheetData>
     <row r="1" spans="3:5" x14ac:dyDescent="0.35">
       <c r="C1" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="D1" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="2" spans="3:5" x14ac:dyDescent="0.35">
       <c r="C2" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="D2" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
     </row>
     <row r="3" spans="3:5" x14ac:dyDescent="0.35">
       <c r="C3" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="D3" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
     </row>
     <row r="4" spans="3:5" x14ac:dyDescent="0.35">
       <c r="C4" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="D4" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
     </row>
     <row r="5" spans="3:5" x14ac:dyDescent="0.35">
       <c r="C5" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="D5" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
     </row>
     <row r="6" spans="3:5" x14ac:dyDescent="0.35">
       <c r="C6" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="E6">
         <v>2</v>
@@ -1608,52 +2022,52 @@
     </row>
     <row r="7" spans="3:5" x14ac:dyDescent="0.35">
       <c r="C7" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="E7" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
     </row>
     <row r="8" spans="3:5" x14ac:dyDescent="0.35">
       <c r="C8" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="9" spans="3:5" x14ac:dyDescent="0.35">
       <c r="C9" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="D9" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
     </row>
     <row r="10" spans="3:5" x14ac:dyDescent="0.35">
       <c r="C10" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="D10" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
     </row>
     <row r="11" spans="3:5" x14ac:dyDescent="0.35">
       <c r="C11" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="D11" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
     </row>
     <row r="12" spans="3:5" x14ac:dyDescent="0.35">
       <c r="C12" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="D12" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
     </row>
     <row r="13" spans="3:5" x14ac:dyDescent="0.35">
       <c r="C13" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="E13">
         <v>1</v>
@@ -1661,26 +2075,26 @@
     </row>
     <row r="14" spans="3:5" x14ac:dyDescent="0.35">
       <c r="C14" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="D14" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
     </row>
     <row r="15" spans="3:5" x14ac:dyDescent="0.35">
       <c r="C15" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="D15" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
     </row>
     <row r="16" spans="3:5" x14ac:dyDescent="0.35">
       <c r="C16" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="D16" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="E16" t="str">
         <f>'dt_Initial Data Entry'!$B$1</f>
@@ -1689,36 +2103,14 @@
     </row>
     <row r="17" spans="3:5" x14ac:dyDescent="0.35">
       <c r="C17" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="D17" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="E17" t="str">
         <f>'dt_Initial Data Entry'!$B$1</f>
         <v>KODE PROGRAM</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:B1"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <cols>
-    <col min="1" max="1" width="11.54296875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="6.6328125" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A1" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>11</v>
       </c>
     </row>
   </sheetData>

--- a/src/main/resources/Test Datatable.xlsx
+++ b/src/main/resources/Test Datatable.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\KERJA\Intellij Project\Testing\Testing\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{29699C2F-5249-4E52-A92E-AD6A0F0A6289}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3B1DE275-57DE-48B3-BC71-20DEF19877D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DATA-INFO" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,6 @@
     <sheet name="Inquiry by Status" sheetId="4" r:id="rId6"/>
     <sheet name="WorkFlow-2" sheetId="5" r:id="rId7"/>
     <sheet name="WorkFlow-3" sheetId="7" r:id="rId8"/>
-    <sheet name="Backup" sheetId="8" r:id="rId9"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -44,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="267" uniqueCount="112">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="230" uniqueCount="98">
   <si>
     <t>Start Data</t>
   </si>
@@ -109,15 +108,9 @@
     <t>Skenario Negatif</t>
   </si>
   <si>
-    <t>https://172.18.30.165/LOSBTNLOGIN/Login.aspx?menu=0</t>
-  </si>
-  <si>
     <t>PASSWORD</t>
   </si>
   <si>
-    <t>Batara1234</t>
-  </si>
-  <si>
     <t>set_text</t>
   </si>
   <si>
@@ -142,18 +135,9 @@
     <t>switch_frame</t>
   </si>
   <si>
-    <t>btnMenuInitial</t>
-  </si>
-  <si>
-    <t>btnMenuInitialDataEntry</t>
-  </si>
-  <si>
     <t>iframeFramex</t>
   </si>
   <si>
-    <t>txtBarcodeID</t>
-  </si>
-  <si>
     <t>PARENT FRAME</t>
   </si>
   <si>
@@ -166,18 +150,6 @@
     <t xml:space="preserve"> </t>
   </si>
   <si>
-    <t>btnPilihBarcode</t>
-  </si>
-  <si>
-    <t>btnLastPageNumber</t>
-  </si>
-  <si>
-    <t>btnLastListBarcode</t>
-  </si>
-  <si>
-    <t>btnPilihKodeProgram</t>
-  </si>
-  <si>
     <t>txtKodeProgram</t>
   </si>
   <si>
@@ -190,9 +162,6 @@
     <t>click_replace</t>
   </si>
   <si>
-    <t>btnReplaceKodeProgram</t>
-  </si>
-  <si>
     <t>Yes</t>
   </si>
   <si>
@@ -214,9 +183,6 @@
     <t>Inquiry by Status</t>
   </si>
   <si>
-    <t>BTN9781</t>
-  </si>
-  <si>
     <t>Skenario Positif</t>
   </si>
   <si>
@@ -265,9 +231,6 @@
     <t>No Aplikasi</t>
   </si>
   <si>
-    <t>0073120251208000001</t>
-  </si>
-  <si>
     <t>btnDetailInquiry_Replace</t>
   </si>
   <si>
@@ -341,12 +304,6 @@
   </si>
   <si>
     <t>USER ID/EMAIL</t>
-  </si>
-  <si>
-    <t>loudry.tiransri@bankbsn.co.id</t>
-  </si>
-  <si>
-    <t>Batara12345</t>
   </si>
   <si>
     <t>//android.view.View[@content-desc="SP3K"]</t>
@@ -477,7 +434,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -492,6 +449,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -789,7 +747,7 @@
         <v>1</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>59</v>
+        <v>48</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.35">
@@ -800,7 +758,7 @@
         <v>4</v>
       </c>
       <c r="C2" t="s">
-        <v>77</v>
+        <v>65</v>
       </c>
     </row>
   </sheetData>
@@ -840,25 +798,25 @@
         <v>9</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>98</v>
+        <v>86</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G1" s="2" t="s">
         <v>18</v>
       </c>
       <c r="H1" s="2" t="s">
-        <v>62</v>
+        <v>51</v>
       </c>
       <c r="I1" s="2" t="s">
-        <v>72</v>
+        <v>61</v>
       </c>
       <c r="J1" s="6" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="K1" s="6" t="s">
-        <v>60</v>
+        <v>49</v>
       </c>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.35">
@@ -866,25 +824,17 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="C2" t="s">
-        <v>70</v>
-      </c>
-      <c r="D2" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="E2" s="5" t="s">
-        <v>56</v>
-      </c>
-      <c r="F2" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="G2" s="7"/>
-      <c r="H2" s="7"/>
-      <c r="I2" s="10" t="s">
-        <v>73</v>
-      </c>
+        <v>59</v>
+      </c>
+      <c r="D2" s="12"/>
+      <c r="E2" s="12"/>
+      <c r="F2" s="12"/>
+      <c r="G2" s="12"/>
+      <c r="H2" s="12"/>
+      <c r="I2" s="10"/>
       <c r="J2" s="5"/>
       <c r="K2" s="5"/>
     </row>
@@ -899,7 +849,7 @@
         <v>20</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>83</v>
+        <v>71</v>
       </c>
       <c r="E3" s="7"/>
       <c r="F3" s="7"/>
@@ -907,7 +857,7 @@
         <v>16</v>
       </c>
       <c r="H3" s="8" t="s">
-        <v>64</v>
+        <v>53</v>
       </c>
       <c r="I3" s="8"/>
       <c r="J3" s="5"/>
@@ -918,21 +868,21 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>58</v>
+        <v>47</v>
       </c>
       <c r="C4" t="s">
-        <v>57</v>
+        <v>46</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>83</v>
+        <v>71</v>
       </c>
       <c r="E4" s="7"/>
       <c r="F4" s="7"/>
       <c r="G4" s="5" t="s">
-        <v>85</v>
+        <v>73</v>
       </c>
       <c r="H4" s="8" t="s">
-        <v>63</v>
+        <v>52</v>
       </c>
       <c r="I4" s="8"/>
       <c r="J4" s="5"/>
@@ -943,21 +893,16 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>87</v>
+        <v>75</v>
       </c>
       <c r="C5" t="s">
-        <v>88</v>
-      </c>
-      <c r="E5" s="5" t="s">
-        <v>99</v>
-      </c>
-      <c r="F5" t="s">
-        <v>100</v>
-      </c>
+        <v>76</v>
+      </c>
+      <c r="E5" s="5"/>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.35">
       <c r="L12" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
     </row>
   </sheetData>
@@ -965,7 +910,6 @@
     <hyperlink ref="G3" r:id="rId1" xr:uid="{00241C0A-274B-437D-B403-A316501FCB38}"/>
     <hyperlink ref="D3" r:id="rId2" xr:uid="{7D62ECF8-D0E4-4CD2-95AC-06C4691A1BCE}"/>
     <hyperlink ref="D4" r:id="rId3" xr:uid="{43AD8348-9BA8-417A-9B8C-EFDD14457260}"/>
-    <hyperlink ref="E5" r:id="rId4" xr:uid="{D81C8870-ABF2-434A-829E-B5B74E6590AD}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -989,7 +933,7 @@
         <v>4</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="C1" s="2" t="s">
         <v>5</v>
@@ -1009,7 +953,7 @@
         <v>11</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>49</v>
+        <v>39</v>
       </c>
       <c r="C2" s="4"/>
       <c r="D2" s="4"/>
@@ -1020,31 +964,31 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.35">
       <c r="C3" t="s">
-        <v>86</v>
+        <v>74</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.35">
       <c r="C4" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="D4" t="s">
-        <v>90</v>
+        <v>78</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.35">
       <c r="C5" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="D5" t="s">
-        <v>90</v>
+        <v>78</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.35">
       <c r="C6" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D6" t="s">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="E6" t="str">
         <f>Datatable!$E$1</f>
@@ -1053,10 +997,10 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.35">
       <c r="C7" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D7" t="s">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="E7" t="str">
         <f>Datatable!$F$1</f>
@@ -1065,28 +1009,28 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.35">
       <c r="C8" t="s">
-        <v>97</v>
+        <v>85</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.35">
       <c r="C9" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="D9" t="s">
-        <v>96</v>
+        <v>84</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.35">
       <c r="C10" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="D10" t="s">
-        <v>102</v>
+        <v>88</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.35">
       <c r="C11" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="E11" s="9">
         <v>2</v>
@@ -1094,16 +1038,16 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.35">
       <c r="C12" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="D12" t="s">
-        <v>111</v>
+        <v>97</v>
       </c>
       <c r="E12" s="9"/>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.35">
       <c r="C13" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="E13" s="9">
         <v>2</v>
@@ -1111,15 +1055,15 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.35">
       <c r="C14" t="s">
-        <v>109</v>
+        <v>95</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A15" s="1" t="s">
-        <v>80</v>
+        <v>68</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>49</v>
+        <v>39</v>
       </c>
       <c r="C15" s="4"/>
       <c r="D15" s="4"/>
@@ -1130,65 +1074,65 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.35">
       <c r="C16" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="D16" t="s">
-        <v>105</v>
+        <v>91</v>
       </c>
     </row>
     <row r="17" spans="3:4" x14ac:dyDescent="0.35">
       <c r="C17" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="D17" t="s">
-        <v>106</v>
+        <v>92</v>
       </c>
     </row>
     <row r="18" spans="3:4" x14ac:dyDescent="0.35">
       <c r="C18" t="s">
-        <v>97</v>
+        <v>85</v>
       </c>
     </row>
     <row r="19" spans="3:4" x14ac:dyDescent="0.35">
       <c r="C19" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="D19" t="s">
-        <v>106</v>
+        <v>92</v>
       </c>
     </row>
     <row r="20" spans="3:4" x14ac:dyDescent="0.35">
       <c r="C20" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="D20" t="s">
-        <v>108</v>
+        <v>94</v>
       </c>
     </row>
     <row r="21" spans="3:4" x14ac:dyDescent="0.35">
       <c r="C21" t="s">
-        <v>97</v>
+        <v>85</v>
       </c>
     </row>
     <row r="22" spans="3:4" x14ac:dyDescent="0.35">
       <c r="C22" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="D22" t="s">
-        <v>108</v>
+        <v>94</v>
       </c>
     </row>
     <row r="23" spans="3:4" x14ac:dyDescent="0.35">
       <c r="C23" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="D23" t="s">
-        <v>94</v>
+        <v>82</v>
       </c>
     </row>
     <row r="24" spans="3:4" x14ac:dyDescent="0.35">
       <c r="C24" t="s">
-        <v>109</v>
+        <v>95</v>
       </c>
     </row>
   </sheetData>
@@ -1209,7 +1153,7 @@
         <v>2</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>45</v>
+        <v>36</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.35">
@@ -1217,7 +1161,7 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>46</v>
+        <v>37</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.35">
@@ -1249,74 +1193,74 @@
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="B2" t="s">
-        <v>89</v>
+        <v>77</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="B3" t="s">
-        <v>91</v>
+        <v>79</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="B4" t="s">
-        <v>92</v>
+        <v>80</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>96</v>
+        <v>84</v>
       </c>
       <c r="B5" t="s">
-        <v>93</v>
+        <v>81</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>102</v>
+        <v>88</v>
       </c>
       <c r="B6" t="s">
-        <v>101</v>
+        <v>87</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>105</v>
+        <v>91</v>
       </c>
       <c r="B7" s="11" t="s">
-        <v>103</v>
+        <v>89</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
-        <v>106</v>
+        <v>92</v>
       </c>
       <c r="B8" t="s">
-        <v>104</v>
+        <v>90</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
-        <v>108</v>
+        <v>94</v>
       </c>
       <c r="B9" t="s">
-        <v>107</v>
+        <v>93</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
-        <v>111</v>
+        <v>97</v>
       </c>
       <c r="B10" t="s">
-        <v>110</v>
+        <v>96</v>
       </c>
     </row>
   </sheetData>
@@ -1341,7 +1285,7 @@
         <v>4</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="C1" s="2" t="s">
         <v>5</v>
@@ -1361,7 +1305,7 @@
         <v>11</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>49</v>
+        <v>39</v>
       </c>
       <c r="C2" s="4"/>
       <c r="D2" s="4"/>
@@ -1372,7 +1316,7 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.35">
       <c r="C3" t="s">
-        <v>86</v>
+        <v>74</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.35">
@@ -1391,10 +1335,10 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.35">
       <c r="C6" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D6" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="E6" t="str">
         <f>Datatable!$E$1</f>
@@ -1403,10 +1347,10 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.35">
       <c r="C7" t="s">
+        <v>22</v>
+      </c>
+      <c r="D7" t="s">
         <v>24</v>
-      </c>
-      <c r="D7" t="s">
-        <v>26</v>
       </c>
       <c r="E7" t="str">
         <f>Datatable!$F$1</f>
@@ -1420,18 +1364,18 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.35">
       <c r="C9" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="D9" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.35">
       <c r="C10" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="D10" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.35">
@@ -1441,18 +1385,18 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.35">
       <c r="C12" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="D12" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A13" s="1" t="s">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>49</v>
+        <v>39</v>
       </c>
       <c r="C13" s="4"/>
       <c r="D13" s="4"/>
@@ -1463,42 +1407,42 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.35">
       <c r="C14" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="D14" t="s">
-        <v>68</v>
+        <v>57</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.35">
       <c r="C15" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="E15" t="s">
-        <v>78</v>
+        <v>66</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.35">
       <c r="C16" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="D16" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
     </row>
     <row r="17" spans="3:5" x14ac:dyDescent="0.35">
       <c r="C17" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="D17" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
     </row>
     <row r="18" spans="3:5" x14ac:dyDescent="0.35">
       <c r="C18" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="D18" t="s">
-        <v>69</v>
+        <v>58</v>
       </c>
     </row>
     <row r="19" spans="3:5" x14ac:dyDescent="0.35">
@@ -1508,58 +1452,58 @@
     </row>
     <row r="20" spans="3:5" x14ac:dyDescent="0.35">
       <c r="C20" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="D20" t="s">
-        <v>52</v>
+        <v>42</v>
       </c>
     </row>
     <row r="21" spans="3:5" x14ac:dyDescent="0.35">
       <c r="C21" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="D21" t="s">
-        <v>53</v>
+        <v>43</v>
       </c>
     </row>
     <row r="22" spans="3:5" x14ac:dyDescent="0.35">
       <c r="C22" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="D22" t="s">
-        <v>53</v>
+        <v>43</v>
       </c>
     </row>
     <row r="23" spans="3:5" x14ac:dyDescent="0.35">
       <c r="C23" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="D23" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
     </row>
     <row r="24" spans="3:5" x14ac:dyDescent="0.35">
       <c r="C24" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="D24" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
     </row>
     <row r="25" spans="3:5" x14ac:dyDescent="0.35">
       <c r="C25" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="D25" t="s">
-        <v>54</v>
+        <v>44</v>
       </c>
     </row>
     <row r="26" spans="3:5" x14ac:dyDescent="0.35">
       <c r="C26" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D26" t="s">
-        <v>71</v>
+        <v>60</v>
       </c>
       <c r="E26" t="str">
         <f>Datatable!$I$1</f>
@@ -1568,39 +1512,39 @@
     </row>
     <row r="27" spans="3:5" x14ac:dyDescent="0.35">
       <c r="C27" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="D27" t="s">
-        <v>54</v>
+        <v>44</v>
       </c>
     </row>
     <row r="28" spans="3:5" x14ac:dyDescent="0.35">
       <c r="C28" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="E28" s="9" t="s">
-        <v>79</v>
+        <v>67</v>
       </c>
     </row>
     <row r="29" spans="3:5" x14ac:dyDescent="0.35">
       <c r="C29" t="s">
+        <v>29</v>
+      </c>
+      <c r="E29" t="s">
         <v>31</v>
-      </c>
-      <c r="E29" t="s">
-        <v>36</v>
       </c>
     </row>
     <row r="30" spans="3:5" x14ac:dyDescent="0.35">
       <c r="C30" t="s">
-        <v>84</v>
+        <v>72</v>
       </c>
     </row>
     <row r="31" spans="3:5" x14ac:dyDescent="0.35">
       <c r="C31" t="s">
-        <v>75</v>
+        <v>63</v>
       </c>
       <c r="D31" t="s">
-        <v>76</v>
+        <v>64</v>
       </c>
       <c r="E31" t="str">
         <f>Datatable!$I$1</f>
@@ -1609,74 +1553,74 @@
     </row>
     <row r="32" spans="3:5" x14ac:dyDescent="0.35">
       <c r="C32" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="D32" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.35">
       <c r="C33" t="s">
-        <v>47</v>
+        <v>38</v>
       </c>
       <c r="D33" t="s">
-        <v>74</v>
+        <v>62</v>
       </c>
       <c r="E33" t="s">
-        <v>76</v>
+        <v>64</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.35">
       <c r="C34" t="s">
+        <v>29</v>
+      </c>
+      <c r="E34" t="s">
         <v>31</v>
-      </c>
-      <c r="E34" t="s">
-        <v>36</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.35">
       <c r="C35" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="D35" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.35">
       <c r="C36" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="D36" t="s">
-        <v>82</v>
+        <v>70</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.35">
       <c r="C37" t="s">
+        <v>29</v>
+      </c>
+      <c r="E37" t="s">
         <v>31</v>
-      </c>
-      <c r="E37" t="s">
-        <v>36</v>
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.35">
       <c r="C38" t="s">
-        <v>84</v>
+        <v>72</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.35">
       <c r="C39" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="D39" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A40" s="1" t="s">
-        <v>80</v>
+        <v>68</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>49</v>
+        <v>39</v>
       </c>
       <c r="C40" s="4"/>
       <c r="D40" s="4"/>
@@ -1687,26 +1631,26 @@
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.35">
       <c r="C41" t="s">
+        <v>29</v>
+      </c>
+      <c r="E41" t="s">
         <v>31</v>
-      </c>
-      <c r="E41" t="s">
-        <v>36</v>
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.35">
       <c r="C42" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="D42" t="s">
-        <v>81</v>
+        <v>69</v>
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.35">
       <c r="C43" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="D43" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.35">
@@ -1738,7 +1682,7 @@
         <v>4</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="C1" s="2" t="s">
         <v>5</v>
@@ -1758,7 +1702,7 @@
         <v>11</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>49</v>
+        <v>39</v>
       </c>
       <c r="C2" s="4"/>
       <c r="D2" s="4"/>
@@ -1769,7 +1713,7 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.35">
       <c r="C3" t="s">
-        <v>86</v>
+        <v>74</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.35">
@@ -1791,7 +1735,7 @@
         <v>19</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>49</v>
+        <v>39</v>
       </c>
       <c r="C6" s="4"/>
       <c r="D6" s="4"/>
@@ -1821,7 +1765,7 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.35">
       <c r="C10" t="s">
-        <v>61</v>
+        <v>50</v>
       </c>
       <c r="E10" t="str">
         <f>Datatable!$H$1</f>
@@ -1830,34 +1774,34 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.35">
       <c r="C11" t="s">
-        <v>65</v>
+        <v>54</v>
       </c>
       <c r="E11" t="s">
-        <v>64</v>
+        <v>53</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.35">
       <c r="C12" t="s">
-        <v>67</v>
+        <v>56</v>
       </c>
       <c r="D12" t="s">
-        <v>44</v>
+        <v>35</v>
       </c>
       <c r="E12" s="9" t="s">
-        <v>66</v>
+        <v>55</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.35">
       <c r="C13" t="s">
-        <v>65</v>
+        <v>54</v>
       </c>
       <c r="E13" t="s">
-        <v>63</v>
+        <v>52</v>
       </c>
     </row>
     <row r="44" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B44" s="1" t="s">
-        <v>51</v>
+        <v>41</v>
       </c>
     </row>
   </sheetData>
@@ -1883,7 +1827,7 @@
         <v>4</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="C1" s="2" t="s">
         <v>5</v>
@@ -1903,7 +1847,7 @@
         <v>11</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>49</v>
+        <v>39</v>
       </c>
       <c r="C2" s="4"/>
       <c r="D2" s="4"/>
@@ -1914,7 +1858,7 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.35">
       <c r="C3" t="s">
-        <v>86</v>
+        <v>74</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.35">
@@ -1928,7 +1872,7 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.35">
       <c r="C5" t="s">
-        <v>84</v>
+        <v>72</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.35">
@@ -1936,7 +1880,7 @@
         <v>19</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>49</v>
+        <v>39</v>
       </c>
       <c r="C6" s="4"/>
       <c r="D6" s="4"/>
@@ -1956,161 +1900,7 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.35">
       <c r="C8" t="s">
-        <v>84</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4254AE48-397C-42B8-BD99-22BF9380EC1F}">
-  <dimension ref="C1:E17"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <cols>
-    <col min="3" max="3" width="22" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="3:5" x14ac:dyDescent="0.35">
-      <c r="C1" t="s">
-        <v>27</v>
-      </c>
-      <c r="D1" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="2" spans="3:5" x14ac:dyDescent="0.35">
-      <c r="C2" t="s">
-        <v>29</v>
-      </c>
-      <c r="D2" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="3" spans="3:5" x14ac:dyDescent="0.35">
-      <c r="C3" t="s">
-        <v>27</v>
-      </c>
-      <c r="D3" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="4" spans="3:5" x14ac:dyDescent="0.35">
-      <c r="C4" t="s">
-        <v>31</v>
-      </c>
-      <c r="D4" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="5" spans="3:5" x14ac:dyDescent="0.35">
-      <c r="C5" t="s">
-        <v>29</v>
-      </c>
-      <c r="D5" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="6" spans="3:5" x14ac:dyDescent="0.35">
-      <c r="C6" t="s">
-        <v>37</v>
-      </c>
-      <c r="E6">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="7" spans="3:5" x14ac:dyDescent="0.35">
-      <c r="C7" t="s">
-        <v>31</v>
-      </c>
-      <c r="E7" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="8" spans="3:5" x14ac:dyDescent="0.35">
-      <c r="C8" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="9" spans="3:5" x14ac:dyDescent="0.35">
-      <c r="C9" t="s">
-        <v>27</v>
-      </c>
-      <c r="D9" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="10" spans="3:5" x14ac:dyDescent="0.35">
-      <c r="C10" t="s">
-        <v>29</v>
-      </c>
-      <c r="D10" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="11" spans="3:5" x14ac:dyDescent="0.35">
-      <c r="C11" t="s">
-        <v>27</v>
-      </c>
-      <c r="D11" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="12" spans="3:5" x14ac:dyDescent="0.35">
-      <c r="C12" t="s">
-        <v>27</v>
-      </c>
-      <c r="D12" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="13" spans="3:5" x14ac:dyDescent="0.35">
-      <c r="C13" t="s">
-        <v>37</v>
-      </c>
-      <c r="E13">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="14" spans="3:5" x14ac:dyDescent="0.35">
-      <c r="C14" t="s">
-        <v>27</v>
-      </c>
-      <c r="D14" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="15" spans="3:5" x14ac:dyDescent="0.35">
-      <c r="C15" t="s">
-        <v>29</v>
-      </c>
-      <c r="D15" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="16" spans="3:5" x14ac:dyDescent="0.35">
-      <c r="C16" t="s">
-        <v>24</v>
-      </c>
-      <c r="D16" t="s">
-        <v>44</v>
-      </c>
-      <c r="E16" t="str">
-        <f>'dt_Initial Data Entry'!$B$1</f>
-        <v>KODE PROGRAM</v>
-      </c>
-    </row>
-    <row r="17" spans="3:5" x14ac:dyDescent="0.35">
-      <c r="C17" t="s">
-        <v>47</v>
-      </c>
-      <c r="D17" t="s">
-        <v>48</v>
-      </c>
-      <c r="E17" t="str">
-        <f>'dt_Initial Data Entry'!$B$1</f>
-        <v>KODE PROGRAM</v>
+        <v>72</v>
       </c>
     </row>
   </sheetData>
